--- a/exports/SAGILITY_full_report.xlsx
+++ b/exports/SAGILITY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45657.55208333334</v>
+        <v>45658.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>50.45</v>
+        <v>47.92</v>
       </c>
       <c r="I2" t="n">
         <v>48.60459793583802</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
-        <v>80.56999999999999</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>0.64</v>
@@ -555,7 +578,7 @@
         <v>4.79</v>
       </c>
       <c r="N2" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
       <c r="O2" t="n">
         <v>-2.82</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.75</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>51.7</v>
+        <v>53.87</v>
       </c>
       <c r="I3" t="n">
         <v>53.32485227338031</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.89</v>
+        <v>-12.42</v>
       </c>
       <c r="L3" t="n">
         <v>13.25</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.57</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>49.1</v>
+        <v>48.55</v>
       </c>
       <c r="I4" t="n">
         <v>48.98340633891582</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.85</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>12.2</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.77</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>47.73</v>
+        <v>49.99</v>
       </c>
       <c r="I5" t="n">
         <v>48.17636147696214</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>1.69</v>
+        <v>-2.97</v>
       </c>
       <c r="L5" t="n">
         <v>4.61</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>12.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>49.98</v>
+        <v>48.56</v>
       </c>
       <c r="I6" t="n">
         <v>49.33308231813311</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02</v>
+        <v>-2.86</v>
       </c>
       <c r="L6" t="n">
         <v>6.78</v>
       </c>
       <c r="M6" t="n">
-        <v>2.04</v>
+        <v>3.46</v>
       </c>
       <c r="N6" t="n">
         <v>4.76</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.03</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>39.88</v>
+        <v>41.86</v>
       </c>
       <c r="I7" t="n">
         <v>41.69234368346022</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K7" t="n">
-        <v>17.87</v>
+        <v>13.8</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.85</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>40.55</v>
+        <v>39.8</v>
       </c>
       <c r="I8" t="n">
         <v>40.40222272994622</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.13</v>
+        <v>-4.92</v>
       </c>
       <c r="L8" t="n">
-        <v>3.68</v>
+        <v>5.16</v>
       </c>
       <c r="M8" t="n">
         <v>0.26</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.57</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>41</v>
+        <v>42.87</v>
       </c>
       <c r="I9" t="n">
         <v>42.74416040828282</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.02</v>
+        <v>-7.71</v>
       </c>
       <c r="L9" t="n">
-        <v>5.53</v>
+        <v>7.71</v>
       </c>
       <c r="M9" t="n">
-        <v>0.46</v>
+        <v>2.68</v>
       </c>
       <c r="N9" t="n">
-        <v>3.42</v>
+        <v>4.56</v>
       </c>
       <c r="O9" t="n">
         <v>-3.47</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>8.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45798.55208333334</v>
+        <v>45799.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>44.2</v>
+        <v>43.65</v>
       </c>
       <c r="I10" t="n">
         <v>43.65789598524799</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="L10" t="n">
         <v>1.96</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
         <v>4.7</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>40.15</v>
+        <v>41.58</v>
       </c>
       <c r="I11" t="n">
         <v>41.16019321901211</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>8.02</v>
+        <v>4.74</v>
       </c>
       <c r="L11" t="n">
         <v>2.04</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45866.38541666666</v>
+        <v>45866.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>43.41</v>
+        <v>41.5</v>
       </c>
       <c r="I12" t="n">
         <v>42.50448062566387</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>-0.19</v>
       </c>
       <c r="L12" t="n">
         <v>4.74</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>42.45</v>
+        <v>45.7</v>
       </c>
       <c r="I13" t="n">
         <v>45.44410658914039</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.29</v>
+        <v>-10.12</v>
       </c>
       <c r="L13" t="n">
-        <v>6.67</v>
+        <v>12.29</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.82</v>
+        <v>9.82</v>
       </c>
       <c r="O13" t="n">
         <v>-5.36</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.87</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>43.04</v>
+        <v>42.21</v>
       </c>
       <c r="I14" t="n">
         <v>42.66478556261431</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.82</v>
+        <v>-7.64</v>
       </c>
       <c r="L14" t="n">
-        <v>7.05</v>
+        <v>7.86</v>
       </c>
       <c r="M14" t="n">
         <v>0.75</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.18</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>43.94</v>
+        <v>44.88</v>
       </c>
       <c r="I15" t="n">
         <v>44.85703937799472</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.1</v>
+        <v>-6.33</v>
       </c>
       <c r="L15" t="n">
-        <v>4.12</v>
+        <v>7.37</v>
       </c>
       <c r="M15" t="n">
         <v>0.26</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.77</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>44.64</v>
+        <v>43.04</v>
       </c>
       <c r="I16" t="n">
         <v>43.63563487593026</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.53</v>
+        <v>-4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.14</v>
+        <v>4.97</v>
       </c>
       <c r="M16" t="n">
         <v>2.37</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45939.38541666666</v>
+        <v>45939.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>44.28</v>
+        <v>45.25</v>
       </c>
       <c r="I17" t="n">
         <v>45.17855545509158</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.88</v>
+        <v>-5.13</v>
       </c>
       <c r="L17" t="n">
         <v>5.95</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45980.55208333334</v>
+        <v>45981.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>50.5</v>
+        <v>49.56</v>
       </c>
       <c r="I18" t="n">
         <v>50.11954610059811</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>11.6</v>
+        <v>9.52</v>
       </c>
       <c r="L18" t="n">
         <v>2.74</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.67</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>50.85</v>
+        <v>51.74</v>
       </c>
       <c r="I19" t="n">
         <v>50.99096670894183</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.6</v>
+        <v>-4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>4.12</v>
+        <v>7.55</v>
       </c>
       <c r="M19" t="n">
         <v>0.95</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.05</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>50.86</v>
+        <v>50.15</v>
       </c>
       <c r="I20" t="n">
         <v>50.46645487553954</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7</v>
+        <v>-3.07</v>
       </c>
       <c r="L20" t="n">
-        <v>2.76</v>
+        <v>4.02</v>
       </c>
       <c r="M20" t="n">
         <v>0.57</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.93</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>51.45</v>
+        <v>53.21</v>
       </c>
       <c r="I21" t="n">
         <v>52.7123999761907</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.59</v>
+        <v>-6.1</v>
       </c>
       <c r="L21" t="n">
-        <v>3.07</v>
+        <v>6.58</v>
       </c>
       <c r="M21" t="n">
         <v>0.12</v>
       </c>
       <c r="N21" t="n">
-        <v>1.28</v>
+        <v>3.56</v>
       </c>
       <c r="O21" t="n">
         <v>-1.96</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>52</v>
+        <v>49.91</v>
       </c>
       <c r="I22" t="n">
         <v>50.78901249499561</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.27</v>
+        <v>-6.2</v>
       </c>
       <c r="L22" t="n">
-        <v>4.17</v>
+        <v>7.72</v>
       </c>
       <c r="M22" t="n">
         <v>0.36</v>
       </c>
       <c r="N22" t="n">
-        <v>3.69</v>
+        <v>5.02</v>
       </c>
       <c r="O22" t="n">
         <v>3.56</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.36</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>39.28</v>
+        <v>42.51</v>
       </c>
       <c r="I23" t="n">
         <v>42.13685460166672</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K23" t="n">
-        <v>21.3</v>
+        <v>14.83</v>
       </c>
       <c r="L23" t="n">
         <v>7.59</v>
@@ -1752,7 +2027,7 @@
         <v>5.73</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>4.84</v>
       </c>
       <c r="O23" t="n">
         <v>-5.02</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>17.64</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>39</v>
+        <v>35.97</v>
       </c>
       <c r="I24" t="n">
         <v>36.69499299538496</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.26</v>
+        <v>-15.38</v>
       </c>
       <c r="L24" t="n">
-        <v>12.7</v>
+        <v>15.71</v>
       </c>
       <c r="M24" t="n">
         <v>3.26</v>
       </c>
       <c r="N24" t="n">
-        <v>4.91</v>
+        <v>6.79</v>
       </c>
       <c r="O24" t="n">
         <v>4.84</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>15.04</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46108.38541666666</v>
+        <v>46108.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>40.31</v>
+        <v>42.41</v>
       </c>
       <c r="I25" t="n">
         <v>40.70477470741267</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-12.07</v>
+        <v>-17.9</v>
       </c>
       <c r="L25" t="n">
-        <v>13.26</v>
+        <v>18.71</v>
       </c>
       <c r="M25" t="n">
         <v>3.65</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.27</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46157.38541666666</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>42.2</v>
+        <v>41.93</v>
       </c>
       <c r="I26" t="n">
         <v>42.06445216589351</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5</v>
+        <v>-1.13</v>
       </c>
       <c r="L26" t="n">
         <v>6.74</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.76</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46204.55208333334</v>
+        <v>46205.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>39.69</v>
+        <v>41.32</v>
       </c>
       <c r="I27" t="n">
         <v>41.29612815420022</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>5.34</v>
+        <v>1.45</v>
       </c>
       <c r="L27" t="n">
         <v>3.7</v>
@@ -1980,7 +2303,7 @@
         <v>2.18</v>
       </c>
       <c r="N27" t="n">
-        <v>3.03</v>
+        <v>4.54</v>
       </c>
       <c r="O27" t="n">
         <v>-2.47</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>42.67</v>
+        <v>42.11</v>
       </c>
       <c r="I28" t="n">
         <v>42.28598546514088</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
-        <v>3.27</v>
+        <v>1.91</v>
       </c>
       <c r="L28" t="n">
         <v>3.61</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.24</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>43.25</v>
+        <v>44.34</v>
       </c>
       <c r="I29" t="n">
         <v>44.09908488303415</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.71</v>
+        <v>-5.3</v>
       </c>
       <c r="L29" t="n">
-        <v>4.49</v>
+        <v>9.48</v>
       </c>
       <c r="M29" t="n">
         <v>0.33</v>
       </c>
       <c r="N29" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O29" t="n">
         <v>-0.77</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46275.38541666666</v>
+        <v>46275.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>44.44</v>
+        <v>44.36</v>
       </c>
       <c r="I30" t="n">
         <v>44.36555260661208</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="L30" t="n">
         <v>2.35</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.97</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>44.1</v>
+        <v>45.55</v>
       </c>
       <c r="I31" t="n">
         <v>44.92004793127258</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>0.59</v>
+        <v>-2.68</v>
       </c>
       <c r="L31" t="n">
         <v>5.28</v>
@@ -2208,7 +2579,7 @@
         <v>1.81</v>
       </c>
       <c r="N31" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="O31" t="n">
         <v>-1.64</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2268,6 +2651,12 @@
       <c r="Q32" t="n">
         <v>18</v>
       </c>
+      <c r="R32" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3214,7 +3603,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="6">
@@ -3224,7 +3613,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -3234,7 +3623,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -3244,7 +3633,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3254,7 +3643,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.4</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10">
@@ -3264,7 +3653,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.7</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="11">
@@ -3304,7 +3693,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.89</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3314,7 +3703,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.81</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="16">
@@ -3324,7 +3713,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.98</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="17">
@@ -3334,7 +3723,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80.56999999999999</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -3344,7 +3733,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -3354,7 +3743,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.43</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="20">
@@ -3364,7 +3753,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.55</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="21">
@@ -3374,7 +3763,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.26</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="22">
@@ -3384,7 +3773,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -3394,7 +3783,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3404,7 +3793,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="25">
@@ -3424,7 +3813,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.95</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="27">
@@ -3434,7 +3823,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.81</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="28">
@@ -3444,7 +3833,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
